--- a/Plano_de_Testes_WebApp_Sucesso_Academico.xlsx
+++ b/Plano_de_Testes_WebApp_Sucesso_Academico.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amorimriki/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amorimriki/Documents/GitHub/Projeto-I-PSA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8939F2-2CA1-3C46-95BD-AAEC3850C9B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77BF691-23AF-A944-A637-CC7AA30843A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="53">
   <si>
     <t>ID do Teste</t>
   </si>
@@ -46,9 +46,6 @@
     <t>Passou? (Sim/Não)</t>
   </si>
   <si>
-    <t>Observações</t>
-  </si>
-  <si>
     <t>TST001</t>
   </si>
   <si>
@@ -70,27 +67,6 @@
     <t>TST007</t>
   </si>
   <si>
-    <t>Validação dos campos de input no frontend</t>
-  </si>
-  <si>
-    <t>Envio de dados válidos para a API e receção da previsão</t>
-  </si>
-  <si>
-    <t>Envio de dados incompletos para verificar tratamento de erro</t>
-  </si>
-  <si>
-    <t>Verificar integração frontend + backend + modelo</t>
-  </si>
-  <si>
-    <t>Avaliar usabilidade e clareza dos campos no UI</t>
-  </si>
-  <si>
-    <t>Testar carga com múltiplos pedidos simultâneos</t>
-  </si>
-  <si>
-    <t>Verificar se o modelo lida com categorias desconhecidas</t>
-  </si>
-  <si>
     <t>Funcional</t>
   </si>
   <si>
@@ -158,6 +134,57 @@
   </si>
   <si>
     <t>Modelo responde com fallback ou erro controlado</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Obriga a escolher os valores das listas. Não aceita campos vazios. Começa com valores default.</t>
+  </si>
+  <si>
+    <t>Não permite enviar dados incompletos. Em caso de dados inválidos assume como erro na previsão.</t>
+  </si>
+  <si>
+    <t>Simples. Agradável. Interativa. Funcional.</t>
+  </si>
+  <si>
+    <t>O modelo não aceita categorias desconhecidas. A validação pela interface protege essa o modelo dessas situações.</t>
+  </si>
+  <si>
+    <t>Teste de 10 segundos em clique constante.</t>
+  </si>
+  <si>
+    <t>INFO:     127.0.0.1:61626 - "POST /predict-file?encoded=true HTTP/1.1" 200 OK.</t>
+  </si>
+  <si>
+    <t>INFO:     127.0.0.1:62348 - "GET /historico HTTP/1.1" 200 OK
+INFO:     127.0.0.1:62348 - "GET /historico/0 HTTP/1.1" 200 OK
+INFO:     127.0.0.1:62350 - "GET /historico/9 HTTP/1.1" 200 OK
+INFO:     127.0.0.1:62350 - "OPTIONS /historico/9 HTTP/1.1" 200 OK
+INFO:     127.0.0.1:62350 - "DELETE /historico/9 HTTP/1.1" 200 OK
+INFO:     127.0.0.1:62356 - "POST /predict-file?encoded=true HTTP/1.1" 200 OK
+INFO:     127.0.0.1:62411 - "POST /predict-json?modelo=mlp_model HTTP/1.1" 200 OK</t>
+  </si>
+  <si>
+    <t>Envio de dados incompletos para verificar tratamento de erro.</t>
+  </si>
+  <si>
+    <t>Envio de dados válidos para a API e receção da previsão.</t>
+  </si>
+  <si>
+    <t>Validação dos campos de input no frontend.</t>
+  </si>
+  <si>
+    <t>Verificar integração frontend + backend + modelo.</t>
+  </si>
+  <si>
+    <t>Avaliar usabilidade e clareza dos campos no UI.</t>
+  </si>
+  <si>
+    <t>Testar carga com múltiplos pedidos simultâneos.</t>
+  </si>
+  <si>
+    <t>Verificar se o modelo lida com categorias desconhecidas.</t>
   </si>
 </sst>
 </file>
@@ -216,10 +243,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,190 +570,472 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.5" customWidth="1"/>
+    <col min="7" max="7" width="68.1640625" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="82" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="4"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="55" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="112" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="F14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="F17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E20" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="F20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="H20" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F8" t="s">
-        <v>45</v>
-      </c>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="7"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="62" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>